--- a/database/event/3954/event_3954_evp_summary.xlsx
+++ b/database/event/3954/event_3954_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.876</v>
+        <v>5.8697</v>
       </c>
       <c r="C2" t="n">
-        <v>3.3619</v>
+        <v>3.3583</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9524</v>
+        <v>1.8946</v>
       </c>
       <c r="E2" t="n">
-        <v>5.876</v>
+        <v>5.8697</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6822</v>
+        <v>1.6759</v>
       </c>
       <c r="G2" t="n">
         <v>4.1938</v>
       </c>
       <c r="H2" t="n">
-        <v>1.6822</v>
+        <v>1.6759</v>
       </c>
       <c r="I2" t="n">
         <v>1.69</v>
@@ -548,7 +548,7 @@
         <v>3.159</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8092</v>
+        <v>1.7558</v>
       </c>
       <c r="E3" t="n">
         <v>5.5214</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.1995</v>
+        <v>5.3396</v>
       </c>
       <c r="C4" t="n">
-        <v>2.9748</v>
+        <v>3.055</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6791</v>
+        <v>1.6834</v>
       </c>
       <c r="E4" t="n">
-        <v>5.1995</v>
+        <v>5.3396</v>
       </c>
       <c r="F4" t="n">
-        <v>4.3062</v>
+        <v>4.4463</v>
       </c>
       <c r="G4" t="n">
         <v>0.8933</v>
       </c>
       <c r="H4" t="n">
-        <v>4.7644</v>
+        <v>5.328</v>
       </c>
       <c r="I4" t="n">
-        <v>3.8617</v>
+        <v>4.3185</v>
       </c>
       <c r="J4" t="n">
         <v>0.8933</v>
@@ -621,7 +621,7 @@
         <v>94</v>
       </c>
       <c r="M4" t="n">
-        <v>4.755</v>
+        <v>5.2118</v>
       </c>
       <c r="N4" t="n">
         <v>254</v>
@@ -630,93 +630,93 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.6351</v>
+        <v>5.2458</v>
       </c>
       <c r="C5" t="n">
-        <v>2.6519</v>
+        <v>3.0013</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4511</v>
+        <v>1.646</v>
       </c>
       <c r="E5" t="n">
-        <v>4.6351</v>
+        <v>5.2458</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8125</v>
+        <v>2.7868</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8226</v>
+        <v>2.459</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8125</v>
+        <v>2.7868</v>
       </c>
       <c r="I5" t="n">
-        <v>1.821</v>
+        <v>2.7868</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8226</v>
+        <v>2.459</v>
       </c>
       <c r="K5" t="n">
-        <v>184</v>
+        <v>122</v>
       </c>
       <c r="L5" t="n">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="M5" t="n">
-        <v>4.6436</v>
+        <v>5.2458</v>
       </c>
       <c r="N5" t="n">
-        <v>394</v>
+        <v>339</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.4568</v>
+        <v>4.6284</v>
       </c>
       <c r="C6" t="n">
-        <v>2.5499</v>
+        <v>2.6481</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3791</v>
+        <v>1.4</v>
       </c>
       <c r="E6" t="n">
-        <v>4.4568</v>
+        <v>4.6284</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9978</v>
+        <v>1.8058</v>
       </c>
       <c r="G6" t="n">
-        <v>2.459</v>
+        <v>2.8226</v>
       </c>
       <c r="H6" t="n">
-        <v>1.9978</v>
+        <v>1.8058</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9978</v>
+        <v>1.821</v>
       </c>
       <c r="J6" t="n">
-        <v>2.459</v>
+        <v>2.8226</v>
       </c>
       <c r="K6" t="n">
-        <v>122</v>
+        <v>184</v>
       </c>
       <c r="L6" t="n">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="M6" t="n">
-        <v>4.4568</v>
+        <v>4.6436</v>
       </c>
       <c r="N6" t="n">
-        <v>339</v>
+        <v>394</v>
       </c>
     </row>
     <row r="7">
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.439</v>
+        <v>4.4169</v>
       </c>
       <c r="C7" t="n">
-        <v>2.5397</v>
+        <v>2.5271</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3719</v>
+        <v>1.3158</v>
       </c>
       <c r="E7" t="n">
-        <v>4.439</v>
+        <v>4.4169</v>
       </c>
       <c r="F7" t="n">
-        <v>4.439</v>
+        <v>4.4169</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>4.6573</v>
+        <v>4.6226</v>
       </c>
       <c r="I7" t="n">
         <v>4.7007</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.3557</v>
+        <v>4.3782</v>
       </c>
       <c r="C8" t="n">
-        <v>2.4921</v>
+        <v>2.5049</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3382</v>
+        <v>1.3004</v>
       </c>
       <c r="E8" t="n">
-        <v>4.3557</v>
+        <v>4.3782</v>
       </c>
       <c r="F8" t="n">
-        <v>3.4906</v>
+        <v>3.5131</v>
       </c>
       <c r="G8" t="n">
         <v>0.8651</v>
       </c>
       <c r="H8" t="n">
-        <v>3.4906</v>
+        <v>3.5131</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8292</v>
+        <v>2.8475</v>
       </c>
       <c r="J8" t="n">
         <v>0.8651</v>
@@ -805,7 +805,7 @@
         <v>60</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6943</v>
+        <v>3.7126</v>
       </c>
       <c r="N8" t="n">
         <v>234</v>
@@ -824,7 +824,7 @@
         <v>2.4369</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2993</v>
+        <v>1.253</v>
       </c>
       <c r="E9" t="n">
         <v>4.2593</v>
@@ -870,7 +870,7 @@
         <v>2.3928</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2682</v>
+        <v>1.2223</v>
       </c>
       <c r="E10" t="n">
         <v>4.1823</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.8851</v>
+        <v>4.0139</v>
       </c>
       <c r="C11" t="n">
-        <v>2.2228</v>
+        <v>2.2965</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1481</v>
+        <v>1.1552</v>
       </c>
       <c r="E11" t="n">
-        <v>3.8851</v>
+        <v>4.0139</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6313</v>
+        <v>1.7601</v>
       </c>
       <c r="G11" t="n">
         <v>2.2538</v>
       </c>
       <c r="H11" t="n">
-        <v>1.6313</v>
+        <v>1.7601</v>
       </c>
       <c r="I11" t="n">
-        <v>1.6389</v>
+        <v>1.7749</v>
       </c>
       <c r="J11" t="n">
         <v>2.2538</v>
@@ -943,7 +943,7 @@
         <v>210</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8927</v>
+        <v>4.0287</v>
       </c>
       <c r="N11" t="n">
         <v>394</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.6802</v>
+        <v>3.8434</v>
       </c>
       <c r="C12" t="n">
-        <v>2.1056</v>
+        <v>2.1989</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0654</v>
+        <v>1.0873</v>
       </c>
       <c r="E12" t="n">
-        <v>3.6802</v>
+        <v>3.8434</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3283</v>
+        <v>-0.1651</v>
       </c>
       <c r="G12" t="n">
         <v>4.0085</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3283</v>
+        <v>-0.1651</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3283</v>
+        <v>-0.1651</v>
       </c>
       <c r="J12" t="n">
         <v>4.0085</v>
@@ -989,7 +989,7 @@
         <v>217</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6802</v>
+        <v>3.8434</v>
       </c>
       <c r="N12" t="n">
         <v>339</v>
@@ -1008,7 +1008,7 @@
         <v>2.085</v>
       </c>
       <c r="D13" t="n">
-        <v>1.0509</v>
+        <v>1.008</v>
       </c>
       <c r="E13" t="n">
         <v>3.6443</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.5156</v>
+        <v>3.4792</v>
       </c>
       <c r="C14" t="n">
-        <v>2.0114</v>
+        <v>1.9906</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9989</v>
+        <v>0.9422</v>
       </c>
       <c r="E14" t="n">
-        <v>3.5156</v>
+        <v>3.4792</v>
       </c>
       <c r="F14" t="n">
-        <v>3.2704</v>
+        <v>3.234</v>
       </c>
       <c r="G14" t="n">
         <v>0.2452</v>
       </c>
       <c r="H14" t="n">
-        <v>3.2704</v>
+        <v>3.234</v>
       </c>
       <c r="I14" t="n">
         <v>3.3163</v>
@@ -1100,7 +1100,7 @@
         <v>1.8271</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8687</v>
+        <v>0.8283</v>
       </c>
       <c r="E15" t="n">
         <v>3.1934</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.1096</v>
+        <v>3.0864</v>
       </c>
       <c r="C16" t="n">
-        <v>1.7791</v>
+        <v>1.7658</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8348</v>
+        <v>0.7857</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1096</v>
+        <v>3.0864</v>
       </c>
       <c r="F16" t="n">
-        <v>3.1096</v>
+        <v>3.0864</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3.1096</v>
+        <v>3.0864</v>
       </c>
       <c r="I16" t="n">
         <v>3.1386</v>
@@ -1182,231 +1182,231 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LOGAN</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.9897</v>
+        <v>3.0436</v>
       </c>
       <c r="C17" t="n">
-        <v>1.7105</v>
+        <v>1.7414</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7864</v>
+        <v>0.7687</v>
       </c>
       <c r="E17" t="n">
-        <v>2.9897</v>
+        <v>3.0436</v>
       </c>
       <c r="F17" t="n">
-        <v>3.9897</v>
+        <v>3.0436</v>
       </c>
       <c r="G17" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>3.9897</v>
+        <v>3.0436</v>
       </c>
       <c r="I17" t="n">
-        <v>4.0456</v>
+        <v>3.0692</v>
       </c>
       <c r="J17" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>269</v>
+        <v>184</v>
       </c>
       <c r="L17" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.0456</v>
+        <v>3.0692</v>
       </c>
       <c r="N17" t="n">
-        <v>346</v>
+        <v>184</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>suNny</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.96</v>
+        <v>3.0208</v>
       </c>
       <c r="C18" t="n">
-        <v>1.6935</v>
+        <v>1.7283</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7744</v>
+        <v>0.7596000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>2.96</v>
+        <v>3.0208</v>
       </c>
       <c r="F18" t="n">
-        <v>2.96</v>
+        <v>3.1693</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-0.1485</v>
       </c>
       <c r="H18" t="n">
-        <v>2.96</v>
+        <v>3.1693</v>
       </c>
       <c r="I18" t="n">
-        <v>2.9738</v>
+        <v>3.25</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-0.1485</v>
       </c>
       <c r="K18" t="n">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9738</v>
+        <v>3.1015</v>
       </c>
       <c r="N18" t="n">
-        <v>184</v>
+        <v>251</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>LOGAN</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.6602</v>
+        <v>2.9452</v>
       </c>
       <c r="C19" t="n">
-        <v>1.522</v>
+        <v>1.6851</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6533</v>
+        <v>0.7295</v>
       </c>
       <c r="E19" t="n">
-        <v>2.6602</v>
+        <v>2.9452</v>
       </c>
       <c r="F19" t="n">
-        <v>3.6602</v>
+        <v>3.9452</v>
       </c>
       <c r="G19" t="n">
         <v>-1</v>
       </c>
       <c r="H19" t="n">
-        <v>3.6602</v>
+        <v>3.9452</v>
       </c>
       <c r="I19" t="n">
-        <v>2.9667</v>
+        <v>4.0456</v>
       </c>
       <c r="J19" t="n">
         <v>-1</v>
       </c>
       <c r="K19" t="n">
-        <v>174</v>
+        <v>269</v>
       </c>
       <c r="L19" t="n">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="M19" t="n">
-        <v>1.9667</v>
+        <v>3.0456</v>
       </c>
       <c r="N19" t="n">
-        <v>234</v>
+        <v>346</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.6517</v>
+        <v>2.6602</v>
       </c>
       <c r="C20" t="n">
-        <v>1.5171</v>
+        <v>1.522</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6499</v>
+        <v>0.6159</v>
       </c>
       <c r="E20" t="n">
-        <v>2.6517</v>
+        <v>2.6602</v>
       </c>
       <c r="F20" t="n">
-        <v>2.6517</v>
+        <v>3.6602</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H20" t="n">
-        <v>2.6517</v>
+        <v>3.6602</v>
       </c>
       <c r="I20" t="n">
-        <v>2.6765</v>
+        <v>2.9667</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K20" t="n">
-        <v>282</v>
+        <v>174</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M20" t="n">
-        <v>2.6765</v>
+        <v>1.9667</v>
       </c>
       <c r="N20" t="n">
-        <v>282</v>
+        <v>234</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.3451</v>
+        <v>2.632</v>
       </c>
       <c r="C21" t="n">
-        <v>1.3417</v>
+        <v>1.5059</v>
       </c>
       <c r="D21" t="n">
-        <v>0.526</v>
+        <v>0.6047</v>
       </c>
       <c r="E21" t="n">
-        <v>2.3451</v>
+        <v>2.632</v>
       </c>
       <c r="F21" t="n">
-        <v>3.3451</v>
+        <v>2.632</v>
       </c>
       <c r="G21" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>3.3451</v>
+        <v>2.632</v>
       </c>
       <c r="I21" t="n">
-        <v>3.3921</v>
+        <v>2.6765</v>
       </c>
       <c r="J21" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>201</v>
+        <v>282</v>
       </c>
       <c r="L21" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.3921</v>
+        <v>2.6765</v>
       </c>
       <c r="N21" t="n">
-        <v>251</v>
+        <v>282</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.2717</v>
+        <v>2.6283</v>
       </c>
       <c r="C22" t="n">
-        <v>1.2997</v>
+        <v>1.5037</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4964</v>
+        <v>0.6032</v>
       </c>
       <c r="E22" t="n">
-        <v>2.2717</v>
+        <v>2.6283</v>
       </c>
       <c r="F22" t="n">
-        <v>2.2717</v>
+        <v>2.6283</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.2717</v>
+        <v>2.6283</v>
       </c>
       <c r="I22" t="n">
-        <v>2.2717</v>
+        <v>2.6283</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.2717</v>
+        <v>2.6283</v>
       </c>
       <c r="N22" t="n">
         <v>129</v>
@@ -1458,35 +1458,35 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>suNny</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.2069</v>
+        <v>2.3078</v>
       </c>
       <c r="C23" t="n">
-        <v>1.2626</v>
+        <v>1.3204</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4702</v>
+        <v>0.4755</v>
       </c>
       <c r="E23" t="n">
-        <v>2.2069</v>
+        <v>2.3078</v>
       </c>
       <c r="F23" t="n">
-        <v>2.3554</v>
+        <v>3.3078</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1485</v>
+        <v>-1</v>
       </c>
       <c r="H23" t="n">
-        <v>2.3554</v>
+        <v>3.3078</v>
       </c>
       <c r="I23" t="n">
-        <v>2.3885</v>
+        <v>3.3921</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.1485</v>
+        <v>-1</v>
       </c>
       <c r="K23" t="n">
         <v>201</v>
@@ -1495,7 +1495,7 @@
         <v>50</v>
       </c>
       <c r="M23" t="n">
-        <v>2.24</v>
+        <v>2.3921</v>
       </c>
       <c r="N23" t="n">
         <v>251</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.9694</v>
+        <v>1.943</v>
       </c>
       <c r="C24" t="n">
-        <v>1.1268</v>
+        <v>1.1117</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3742</v>
+        <v>0.3302</v>
       </c>
       <c r="E24" t="n">
-        <v>1.9694</v>
+        <v>1.943</v>
       </c>
       <c r="F24" t="n">
-        <v>2.3624</v>
+        <v>2.336</v>
       </c>
       <c r="G24" t="n">
         <v>-0.393</v>
       </c>
       <c r="H24" t="n">
-        <v>2.3624</v>
+        <v>2.336</v>
       </c>
       <c r="I24" t="n">
         <v>2.3955</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.902</v>
+        <v>1.9258</v>
       </c>
       <c r="C25" t="n">
-        <v>1.0882</v>
+        <v>1.1018</v>
       </c>
       <c r="D25" t="n">
-        <v>0.347</v>
+        <v>0.3233</v>
       </c>
       <c r="E25" t="n">
-        <v>1.902</v>
+        <v>1.9258</v>
       </c>
       <c r="F25" t="n">
-        <v>2.3299</v>
+        <v>2.3537</v>
       </c>
       <c r="G25" t="n">
         <v>-0.4279</v>
       </c>
       <c r="H25" t="n">
-        <v>2.3299</v>
+        <v>2.3537</v>
       </c>
       <c r="I25" t="n">
-        <v>2.3626</v>
+        <v>2.4136</v>
       </c>
       <c r="J25" t="n">
         <v>-0.4279</v>
@@ -1587,7 +1587,7 @@
         <v>77</v>
       </c>
       <c r="M25" t="n">
-        <v>1.9347</v>
+        <v>1.9857</v>
       </c>
       <c r="N25" t="n">
         <v>346</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.8859</v>
+        <v>1.8869</v>
       </c>
       <c r="C26" t="n">
-        <v>1.079</v>
+        <v>1.0796</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3405</v>
+        <v>0.3078</v>
       </c>
       <c r="E26" t="n">
-        <v>1.8859</v>
+        <v>1.8869</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.2445</v>
+        <v>-0.2436</v>
       </c>
       <c r="G26" t="n">
         <v>2.1304</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.2445</v>
+        <v>-0.2436</v>
       </c>
       <c r="I26" t="n">
         <v>-0.2456</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.6673</v>
+        <v>1.7743</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9539</v>
+        <v>1.0151</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2522</v>
+        <v>0.263</v>
       </c>
       <c r="E27" t="n">
-        <v>1.6673</v>
+        <v>1.7743</v>
       </c>
       <c r="F27" t="n">
-        <v>1.9372</v>
+        <v>2.0442</v>
       </c>
       <c r="G27" t="n">
         <v>-0.2699</v>
       </c>
       <c r="H27" t="n">
-        <v>1.9372</v>
+        <v>2.0442</v>
       </c>
       <c r="I27" t="n">
-        <v>1.9644</v>
+        <v>2.0962</v>
       </c>
       <c r="J27" t="n">
         <v>-0.2699</v>
@@ -1679,7 +1679,7 @@
         <v>50</v>
       </c>
       <c r="M27" t="n">
-        <v>1.6945</v>
+        <v>1.8263</v>
       </c>
       <c r="N27" t="n">
         <v>251</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.6026</v>
+        <v>1.7388</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9169</v>
+        <v>0.9948</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2261</v>
+        <v>0.2488</v>
       </c>
       <c r="E28" t="n">
-        <v>1.6026</v>
+        <v>1.7388</v>
       </c>
       <c r="F28" t="n">
-        <v>1.6026</v>
+        <v>1.7388</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.6026</v>
+        <v>1.7388</v>
       </c>
       <c r="I28" t="n">
-        <v>1.6026</v>
+        <v>1.7388</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.6026</v>
+        <v>1.7388</v>
       </c>
       <c r="N28" t="n">
         <v>143</v>
@@ -1744,7 +1744,7 @@
         <v>0.8552999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1826</v>
+        <v>0.1517</v>
       </c>
       <c r="E29" t="n">
         <v>1.495</v>
@@ -1784,25 +1784,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.3935</v>
+        <v>1.3884</v>
       </c>
       <c r="C30" t="n">
-        <v>0.7973</v>
+        <v>0.7944</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1416</v>
+        <v>0.1092</v>
       </c>
       <c r="E30" t="n">
-        <v>1.3935</v>
+        <v>1.3884</v>
       </c>
       <c r="F30" t="n">
-        <v>1.3935</v>
+        <v>1.3884</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.3935</v>
+        <v>1.3884</v>
       </c>
       <c r="I30" t="n">
         <v>1.4</v>
@@ -1826,139 +1826,139 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>xeta</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.2898</v>
+        <v>1.3632</v>
       </c>
       <c r="C31" t="n">
-        <v>0.7379</v>
+        <v>0.7799</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0997</v>
+        <v>0.0992</v>
       </c>
       <c r="E31" t="n">
-        <v>1.2898</v>
+        <v>1.3632</v>
       </c>
       <c r="F31" t="n">
-        <v>1.2898</v>
+        <v>1.3632</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.2898</v>
+        <v>1.3632</v>
       </c>
       <c r="I31" t="n">
-        <v>1.2898</v>
+        <v>1.3632</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>100</v>
+        <v>208</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.2898</v>
+        <v>1.3632</v>
       </c>
       <c r="N31" t="n">
-        <v>100</v>
+        <v>208</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>xeta</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.1713</v>
+        <v>1.2898</v>
       </c>
       <c r="C32" t="n">
-        <v>0.6701</v>
+        <v>0.7379</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0518</v>
+        <v>0.0699</v>
       </c>
       <c r="E32" t="n">
-        <v>1.1713</v>
+        <v>1.2898</v>
       </c>
       <c r="F32" t="n">
-        <v>1.7548</v>
+        <v>1.2898</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.5835</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.7548</v>
+        <v>1.2898</v>
       </c>
       <c r="I32" t="n">
-        <v>1.4223</v>
+        <v>1.2898</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.5835</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>174</v>
+        <v>100</v>
       </c>
       <c r="L32" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.8387999999999999</v>
+        <v>1.2898</v>
       </c>
       <c r="N32" t="n">
-        <v>234</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.1243</v>
+        <v>1.1713</v>
       </c>
       <c r="C33" t="n">
-        <v>0.6433</v>
+        <v>0.6701</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0328</v>
+        <v>0.0227</v>
       </c>
       <c r="E33" t="n">
-        <v>1.1243</v>
+        <v>1.1713</v>
       </c>
       <c r="F33" t="n">
-        <v>1.1243</v>
+        <v>1.7548</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-0.5835</v>
       </c>
       <c r="H33" t="n">
-        <v>1.1243</v>
+        <v>1.7548</v>
       </c>
       <c r="I33" t="n">
-        <v>1.1243</v>
+        <v>1.4223</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>-0.5835</v>
       </c>
       <c r="K33" t="n">
-        <v>208</v>
+        <v>174</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M33" t="n">
-        <v>1.1243</v>
+        <v>0.8387999999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>208</v>
+        <v>234</v>
       </c>
     </row>
     <row r="34">
@@ -1974,7 +1974,7 @@
         <v>0.6372</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0285</v>
+        <v>-0.0002</v>
       </c>
       <c r="E34" t="n">
         <v>1.1137</v>
@@ -2010,1059 +2010,1059 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.0458</v>
+        <v>1.0802</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5983000000000001</v>
+        <v>0.618</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0011</v>
+        <v>-0.0136</v>
       </c>
       <c r="E35" t="n">
-        <v>1.0458</v>
+        <v>1.0802</v>
       </c>
       <c r="F35" t="n">
-        <v>1.7968</v>
+        <v>1.0802</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.751</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.7968</v>
+        <v>1.0802</v>
       </c>
       <c r="I35" t="n">
-        <v>1.822</v>
+        <v>1.0802</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.751</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="L35" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.071</v>
+        <v>1.0802</v>
       </c>
       <c r="N35" t="n">
-        <v>251</v>
+        <v>208</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>nex</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.9955000000000001</v>
+        <v>1.0257</v>
       </c>
       <c r="C36" t="n">
-        <v>0.5696</v>
+        <v>0.5868</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0192</v>
+        <v>-0.0353</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9955000000000001</v>
+        <v>1.0257</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9955000000000001</v>
+        <v>1.7767</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-0.751</v>
       </c>
       <c r="H36" t="n">
-        <v>0.9955000000000001</v>
+        <v>1.7767</v>
       </c>
       <c r="I36" t="n">
-        <v>0.9955000000000001</v>
+        <v>1.822</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>-0.751</v>
       </c>
       <c r="K36" t="n">
-        <v>136</v>
+        <v>201</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M36" t="n">
-        <v>0.9955000000000001</v>
+        <v>1.071</v>
       </c>
       <c r="N36" t="n">
-        <v>136</v>
+        <v>251</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>nex</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.792</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4531</v>
+        <v>0.5696</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1014</v>
+        <v>-0.0473</v>
       </c>
       <c r="E37" t="n">
-        <v>0.792</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>0.792</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.792</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>0.792</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>208</v>
+        <v>136</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.792</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="N37" t="n">
-        <v>208</v>
+        <v>136</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FugLy</t>
+          <t>STYKO</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7728</v>
+        <v>0.9393</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4421</v>
+        <v>0.5374</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1092</v>
+        <v>-0.0697</v>
       </c>
       <c r="E38" t="n">
-        <v>0.7728</v>
+        <v>0.9393</v>
       </c>
       <c r="F38" t="n">
-        <v>0.7728</v>
+        <v>0.9897</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-0.0504</v>
       </c>
       <c r="H38" t="n">
-        <v>0.7728</v>
+        <v>0.9897</v>
       </c>
       <c r="I38" t="n">
-        <v>0.78</v>
+        <v>1.0149</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-0.0504</v>
       </c>
       <c r="K38" t="n">
-        <v>282</v>
+        <v>201</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M38" t="n">
-        <v>0.78</v>
+        <v>0.9644999999999999</v>
       </c>
       <c r="N38" t="n">
-        <v>282</v>
+        <v>251</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>FugLy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7637</v>
+        <v>0.767</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4369</v>
+        <v>0.4388</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1128</v>
+        <v>-0.1383</v>
       </c>
       <c r="E39" t="n">
-        <v>0.7637</v>
+        <v>0.767</v>
       </c>
       <c r="F39" t="n">
-        <v>0.7637</v>
+        <v>0.767</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.7637</v>
+        <v>0.767</v>
       </c>
       <c r="I39" t="n">
-        <v>0.7637</v>
+        <v>0.78</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>208</v>
+        <v>282</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.7637</v>
+        <v>0.78</v>
       </c>
       <c r="N39" t="n">
-        <v>208</v>
+        <v>282</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ALEX</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6334</v>
+        <v>0.7637</v>
       </c>
       <c r="C40" t="n">
-        <v>0.3624</v>
+        <v>0.4369</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1655</v>
+        <v>-0.1397</v>
       </c>
       <c r="E40" t="n">
-        <v>0.6334</v>
+        <v>0.7637</v>
       </c>
       <c r="F40" t="n">
-        <v>0.8073</v>
+        <v>0.7637</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.1739</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.8073</v>
+        <v>0.7637</v>
       </c>
       <c r="I40" t="n">
-        <v>0.8186</v>
+        <v>0.7637</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.1739</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>269</v>
+        <v>208</v>
       </c>
       <c r="L40" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.6447000000000001</v>
+        <v>0.7637</v>
       </c>
       <c r="N40" t="n">
-        <v>346</v>
+        <v>208</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>dazzLe</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5423</v>
+        <v>0.6315</v>
       </c>
       <c r="C41" t="n">
-        <v>0.3103</v>
+        <v>0.3613</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2023</v>
+        <v>-0.1923</v>
       </c>
       <c r="E41" t="n">
-        <v>0.5423</v>
+        <v>0.6315</v>
       </c>
       <c r="F41" t="n">
-        <v>0.5423</v>
+        <v>0.6315</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.5423</v>
+        <v>0.6315</v>
       </c>
       <c r="I41" t="n">
-        <v>0.5448</v>
+        <v>0.6315</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>184</v>
+        <v>129</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.5448</v>
+        <v>0.6315</v>
       </c>
       <c r="N41" t="n">
-        <v>184</v>
+        <v>129</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>yel</t>
+          <t>ALEX</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5313</v>
+        <v>0.6244</v>
       </c>
       <c r="C42" t="n">
-        <v>0.304</v>
+        <v>0.3572</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2067</v>
+        <v>-0.1951</v>
       </c>
       <c r="E42" t="n">
-        <v>0.5313</v>
+        <v>0.6244</v>
       </c>
       <c r="F42" t="n">
-        <v>0.5313</v>
+        <v>0.7983</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>-0.1739</v>
       </c>
       <c r="H42" t="n">
-        <v>0.5313</v>
+        <v>0.7983</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5338000000000001</v>
+        <v>0.8186</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>-0.1739</v>
       </c>
       <c r="K42" t="n">
-        <v>184</v>
+        <v>269</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M42" t="n">
-        <v>0.5338000000000001</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="N42" t="n">
-        <v>184</v>
+        <v>346</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.3076</v>
+        <v>0.5403</v>
       </c>
       <c r="C43" t="n">
-        <v>0.176</v>
+        <v>0.3091</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2971</v>
+        <v>-0.2287</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3076</v>
+        <v>0.5403</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2485</v>
+        <v>0.5403</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0591</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2485</v>
+        <v>0.5403</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2496</v>
+        <v>0.5448</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0591</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
         <v>184</v>
       </c>
       <c r="L43" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.3087</v>
+        <v>0.5448</v>
       </c>
       <c r="N43" t="n">
-        <v>394</v>
+        <v>184</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>yel</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.2759</v>
+        <v>0.5293</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1579</v>
+        <v>0.3028</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3099</v>
+        <v>-0.233</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2759</v>
+        <v>0.5293</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2759</v>
+        <v>0.5293</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2759</v>
+        <v>0.5293</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2759</v>
+        <v>0.5338000000000001</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>143</v>
+        <v>184</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.2759</v>
+        <v>0.5338000000000001</v>
       </c>
       <c r="N44" t="n">
-        <v>143</v>
+        <v>184</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Relyks</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.263</v>
+        <v>0.427</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1505</v>
+        <v>0.2443</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3151</v>
+        <v>-0.2738</v>
       </c>
       <c r="E45" t="n">
-        <v>0.263</v>
+        <v>0.427</v>
       </c>
       <c r="F45" t="n">
-        <v>0.263</v>
+        <v>0.427</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.263</v>
+        <v>0.427</v>
       </c>
       <c r="I45" t="n">
-        <v>0.263</v>
+        <v>0.427</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.263</v>
+        <v>0.427</v>
       </c>
       <c r="N45" t="n">
-        <v>129</v>
+        <v>143</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.2399</v>
+        <v>0.3502</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1373</v>
+        <v>0.2004</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3244</v>
+        <v>-0.3044</v>
       </c>
       <c r="E46" t="n">
-        <v>0.2399</v>
+        <v>0.3502</v>
       </c>
       <c r="F46" t="n">
-        <v>0.2399</v>
+        <v>0.2911</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>0.0591</v>
       </c>
       <c r="H46" t="n">
-        <v>0.2399</v>
+        <v>0.2911</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2399</v>
+        <v>0.2936</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>0.0591</v>
       </c>
       <c r="K46" t="n">
-        <v>208</v>
+        <v>184</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="M46" t="n">
-        <v>0.2399</v>
+        <v>0.3527</v>
       </c>
       <c r="N46" t="n">
-        <v>208</v>
+        <v>394</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STYKO</t>
+          <t>Relyks</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.0848</v>
+        <v>0.2832</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0485</v>
+        <v>0.162</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3871</v>
+        <v>-0.3311</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0848</v>
+        <v>0.2832</v>
       </c>
       <c r="F47" t="n">
-        <v>0.1352</v>
+        <v>0.2832</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.0504</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.1352</v>
+        <v>0.2832</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1371</v>
+        <v>0.2832</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.0504</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>201</v>
+        <v>129</v>
       </c>
       <c r="L47" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.0867</v>
+        <v>0.2832</v>
       </c>
       <c r="N47" t="n">
-        <v>251</v>
+        <v>129</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>dazzLe</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.0751</v>
+        <v>0.2399</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.043</v>
+        <v>0.1373</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4517</v>
+        <v>-0.3483</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.0751</v>
+        <v>0.2399</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.0751</v>
+        <v>0.2399</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.0751</v>
+        <v>0.2399</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.0751</v>
+        <v>0.2399</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>129</v>
+        <v>208</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.0751</v>
+        <v>0.2399</v>
       </c>
       <c r="N48" t="n">
-        <v>129</v>
+        <v>208</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Gratisfaction</t>
+          <t>gade</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.1602</v>
+        <v>0.0645</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.0917</v>
+        <v>0.0369</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4861</v>
+        <v>-0.4182</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.1602</v>
+        <v>0.0645</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.1602</v>
+        <v>0.0645</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.1602</v>
+        <v>0.0645</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1602</v>
+        <v>0.0645</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.1602</v>
+        <v>0.0645</v>
       </c>
       <c r="N49" t="n">
-        <v>104</v>
+        <v>143</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Qikert</t>
+          <t>twist</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.1637</v>
+        <v>-0.0335</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.09370000000000001</v>
+        <v>-0.0192</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4875</v>
+        <v>-0.4573</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.1637</v>
+        <v>-0.0335</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.1637</v>
+        <v>-0.3267</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>0.2932</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.1637</v>
+        <v>-0.3267</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1637</v>
+        <v>-0.2648</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>0.2932</v>
       </c>
       <c r="K50" t="n">
-        <v>77</v>
+        <v>160</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.1637</v>
+        <v>0.02840000000000004</v>
       </c>
       <c r="N50" t="n">
-        <v>77</v>
+        <v>254</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>Gratisfaction</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.1726</v>
+        <v>-0.1602</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.0988</v>
+        <v>-0.0917</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4911</v>
+        <v>-0.5077</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.1726</v>
+        <v>-0.1602</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.1726</v>
+        <v>-0.1602</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.1726</v>
+        <v>-0.1602</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1726</v>
+        <v>-0.1602</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.1726</v>
+        <v>-0.1602</v>
       </c>
       <c r="N51" t="n">
-        <v>81</v>
+        <v>104</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>XigN</t>
+          <t>Qikert</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.3238</v>
+        <v>-0.1637</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.1853</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5522</v>
+        <v>-0.5091</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.3238</v>
+        <v>-0.1637</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.3238</v>
+        <v>-0.1637</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.3238</v>
+        <v>-0.1637</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.3238</v>
+        <v>-0.1637</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.3238</v>
+        <v>-0.1637</v>
       </c>
       <c r="N52" t="n">
-        <v>100</v>
+        <v>77</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>buster</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.3434</v>
+        <v>-0.1726</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.1965</v>
+        <v>-0.0988</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5601</v>
+        <v>-0.5127</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.3434</v>
+        <v>-0.1726</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.3434</v>
+        <v>-0.1726</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.3434</v>
+        <v>-0.1726</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.3434</v>
+        <v>-0.1726</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.3434</v>
+        <v>-0.1726</v>
       </c>
       <c r="N53" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>XigN</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.3555</v>
+        <v>-0.3238</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.2034</v>
+        <v>-0.1853</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.5729</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.3555</v>
+        <v>-0.3238</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.3555</v>
+        <v>-0.3238</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.3555</v>
+        <v>-0.3238</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.3555</v>
+        <v>-0.3238</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.3555</v>
+        <v>-0.3238</v>
       </c>
       <c r="N54" t="n">
-        <v>77</v>
+        <v>100</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>buster</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.4177</v>
+        <v>-0.3434</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.239</v>
+        <v>-0.1965</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5901</v>
+        <v>-0.5807</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.4177</v>
+        <v>-0.3434</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.4177</v>
+        <v>-0.3434</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.4177</v>
+        <v>-0.3434</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.4177</v>
+        <v>-0.3434</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>208</v>
+        <v>77</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.4177</v>
+        <v>-0.3434</v>
       </c>
       <c r="N55" t="n">
-        <v>208</v>
+        <v>77</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>gade</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.4363</v>
+        <v>-0.3555</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.2496</v>
+        <v>-0.2034</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5976</v>
+        <v>-0.5855</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.4363</v>
+        <v>-0.3555</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.4363</v>
+        <v>-0.3555</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.4363</v>
+        <v>-0.3555</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4363</v>
+        <v>-0.3555</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.4363</v>
+        <v>-0.3555</v>
       </c>
       <c r="N56" t="n">
-        <v>143</v>
+        <v>77</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>twist</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.5788</v>
+        <v>-0.4177</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.3312</v>
+        <v>-0.239</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6552</v>
+        <v>-0.6103</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.5788</v>
+        <v>-0.4177</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.872</v>
+        <v>-0.4177</v>
       </c>
       <c r="G57" t="n">
-        <v>0.2932</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.872</v>
+        <v>-0.4177</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.7068</v>
+        <v>-0.4177</v>
       </c>
       <c r="J57" t="n">
-        <v>0.2932</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>160</v>
+        <v>208</v>
       </c>
       <c r="L57" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.4136</v>
+        <v>-0.4177</v>
       </c>
       <c r="N57" t="n">
-        <v>254</v>
+        <v>208</v>
       </c>
     </row>
     <row r="58">
@@ -3078,7 +3078,7 @@
         <v>-0.3446</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6647</v>
+        <v>-0.6839</v>
       </c>
       <c r="E58" t="n">
         <v>-0.6022999999999999</v>
@@ -3124,7 +3124,7 @@
         <v>-0.3589</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6748</v>
+        <v>-0.6938</v>
       </c>
       <c r="E59" t="n">
         <v>-0.6273</v>
@@ -3170,7 +3170,7 @@
         <v>-0.3987</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.7029</v>
+        <v>-0.7216</v>
       </c>
       <c r="E60" t="n">
         <v>-0.6969</v>
@@ -3216,7 +3216,7 @@
         <v>-0.4186</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.717</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="E61" t="n">
         <v>-0.7317</v>
@@ -3262,7 +3262,7 @@
         <v>-0.4245</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7211</v>
+        <v>-0.7395</v>
       </c>
       <c r="E62" t="n">
         <v>-0.7419</v>
@@ -3308,7 +3308,7 @@
         <v>-0.4369</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7299</v>
+        <v>-0.7482</v>
       </c>
       <c r="E63" t="n">
         <v>-0.7637</v>
@@ -3354,7 +3354,7 @@
         <v>-0.4404</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7323</v>
+        <v>-0.7506</v>
       </c>
       <c r="E64" t="n">
         <v>-0.7698</v>
@@ -3400,7 +3400,7 @@
         <v>-0.5039</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7772</v>
+        <v>-0.7948</v>
       </c>
       <c r="E65" t="n">
         <v>-0.8808</v>
@@ -3446,7 +3446,7 @@
         <v>-0.546</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8069</v>
+        <v>-0.8241000000000001</v>
       </c>
       <c r="E66" t="n">
         <v>-0.9543</v>
@@ -3492,7 +3492,7 @@
         <v>-0.5666</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8214</v>
+        <v>-0.8384</v>
       </c>
       <c r="E67" t="n">
         <v>-0.9903</v>
@@ -3538,7 +3538,7 @@
         <v>-0.5824</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8326</v>
+        <v>-0.8495</v>
       </c>
       <c r="E68" t="n">
         <v>-1.018</v>
@@ -3584,7 +3584,7 @@
         <v>-0.595</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8415</v>
+        <v>-0.8582</v>
       </c>
       <c r="E69" t="n">
         <v>-1.04</v>
@@ -3630,7 +3630,7 @@
         <v>-0.5963000000000001</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8424</v>
+        <v>-0.8592</v>
       </c>
       <c r="E70" t="n">
         <v>-1.0423</v>
@@ -3676,7 +3676,7 @@
         <v>-0.6175</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-0.8739</v>
       </c>
       <c r="E71" t="n">
         <v>-1.0793</v>
@@ -3722,7 +3722,7 @@
         <v>-0.721</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9305</v>
+        <v>-0.946</v>
       </c>
       <c r="E72" t="n">
         <v>-1.2602</v>
@@ -3768,7 +3768,7 @@
         <v>-0.768</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9637</v>
+        <v>-0.9787</v>
       </c>
       <c r="E73" t="n">
         <v>-1.3424</v>
@@ -3814,7 +3814,7 @@
         <v>-0.8774999999999999</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0409</v>
+        <v>-1.0549</v>
       </c>
       <c r="E74" t="n">
         <v>-1.5337</v>
@@ -3860,7 +3860,7 @@
         <v>-0.9291</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.0774</v>
+        <v>-1.0909</v>
       </c>
       <c r="E75" t="n">
         <v>-1.6239</v>
@@ -3906,7 +3906,7 @@
         <v>-0.9842</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1163</v>
+        <v>-1.1293</v>
       </c>
       <c r="E76" t="n">
         <v>-1.7203</v>
@@ -3952,7 +3952,7 @@
         <v>-0.9843</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1164</v>
+        <v>-1.1293</v>
       </c>
       <c r="E77" t="n">
         <v>-1.7204</v>
@@ -3998,7 +3998,7 @@
         <v>-0.9845</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.1165</v>
+        <v>-1.1295</v>
       </c>
       <c r="E78" t="n">
         <v>-1.7208</v>
@@ -4038,25 +4038,25 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.8963</v>
+        <v>-1.8892</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.0849</v>
+        <v>-1.0809</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.1874</v>
+        <v>-1.1966</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.8963</v>
+        <v>-1.8892</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.8963</v>
+        <v>-1.8892</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.8963</v>
+        <v>-1.8892</v>
       </c>
       <c r="I79" t="n">
         <v>-1.9051</v>
@@ -4090,7 +4090,7 @@
         <v>-1.7755</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.675</v>
+        <v>-1.6802</v>
       </c>
       <c r="E80" t="n">
         <v>-3.1032</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-3.2984</v>
+        <v>-3.2739</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.8871</v>
+        <v>-1.8731</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.7538</v>
+        <v>-1.7482</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.2984</v>
+        <v>-3.2739</v>
       </c>
       <c r="F81" t="n">
-        <v>-3.2984</v>
+        <v>-3.2739</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-3.2984</v>
+        <v>-3.2739</v>
       </c>
       <c r="I81" t="n">
         <v>-3.3292</v>
